--- a/registros.xlsx
+++ b/registros.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="70">
   <si>
     <t>Fecha</t>
   </si>
@@ -98,6 +98,129 @@
   </si>
   <si>
     <t>10:34</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:43</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>Mónica Guadalupe Alvarez Gudiño</t>
+  </si>
+  <si>
+    <t>21420118</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>23/6/2025</t>
+  </si>
+  <si>
+    <t>Jaime Adrián León Marín</t>
+  </si>
+  <si>
+    <t>23420277</t>
+  </si>
+  <si>
+    <t>Ingenieria Industrial</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>Yuridia Linette Manzo Pardo</t>
+  </si>
+  <si>
+    <t>23420262</t>
+  </si>
+  <si>
+    <t>11:59</t>
+  </si>
+  <si>
+    <t>Bryan Joel Camacho Cervantes</t>
+  </si>
+  <si>
+    <t>23420015</t>
+  </si>
+  <si>
+    <t>Arquitectura</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>Ángel Bryan Gudiño Rodriguez</t>
+  </si>
+  <si>
+    <t>23420097</t>
+  </si>
+  <si>
+    <t>Luis Angel Aguilera García</t>
+  </si>
+  <si>
+    <t>23420100</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>Erick Giovanni Segura Méndez</t>
+  </si>
+  <si>
+    <t>23420088</t>
+  </si>
+  <si>
+    <t>María José Rodríguez Falcón</t>
+  </si>
+  <si>
+    <t>23420087</t>
+  </si>
+  <si>
+    <t>Mayra Daniela Huerta Hernández</t>
+  </si>
+  <si>
+    <t>23420051</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>Sergio Jesús Ochoa Torres</t>
+  </si>
+  <si>
+    <t>22420118</t>
+  </si>
+  <si>
+    <t>Jimena Ibañez Martínez</t>
+  </si>
+  <si>
+    <t>22420041</t>
+  </si>
+  <si>
+    <t>8/8/2025</t>
+  </si>
+  <si>
+    <t>12:41</t>
   </si>
 </sst>
 </file>
@@ -492,14 +615,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="13.2" customWidth="1"/>
     <col min="3" max="3" width="47.2" customWidth="1"/>
     <col min="4" max="4" width="15.13" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="10" width="9.2" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="10" width="9.9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -694,6 +817,646 @@
         <v>15</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
